--- a/grupos/4BLCM - Estadisticos 20212.xlsx
+++ b/grupos/4BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
@@ -215,15 +215,72 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
@@ -248,39 +305,21 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>DE LUNA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -290,9 +329,6 @@
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -326,12 +362,6 @@
     <t>PRADO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
@@ -341,6 +371,9 @@
     <t>SERRANO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -350,9 +383,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
     <t>GASPAR</t>
   </si>
   <si>
@@ -362,9 +392,6 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -380,9 +407,6 @@
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
     <t>AMERICA MICHELLE</t>
   </si>
   <si>
@@ -413,24 +437,18 @@
     <t>ALEXA</t>
   </si>
   <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
     <t>MARIA MAGDALENA</t>
   </si>
   <si>
     <t>IKER</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
     <t>IVONNE SHERLINE</t>
   </si>
   <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
     <t>RITA ALEJANDRA</t>
   </si>
   <si>
@@ -440,12 +458,6 @@
     <t>MARISOL</t>
   </si>
   <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
     <t>DIANA SARAY</t>
   </si>
   <si>
@@ -458,9 +470,6 @@
     <t>NAOMI</t>
   </si>
   <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
     <t>JOSELIN GUADALUPE</t>
   </si>
   <si>
@@ -468,15 +477,6 @@
   </si>
   <si>
     <t>LAURA IVETTE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
   </si>
 </sst>
 </file>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -1047,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1073,7 +1073,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1136,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -1162,7 +1162,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -1225,7 +1225,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>8</v>
@@ -1251,7 +1251,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1340,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1403,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1492,7 +1492,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>10</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1696,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1937,7 +1937,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1963,7 +1963,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>8</v>
@@ -2026,7 +2026,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -2052,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -2115,7 +2115,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -2204,7 +2204,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2230,7 +2230,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -2293,7 +2293,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2319,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -2497,7 +2497,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>6</v>
@@ -2560,7 +2560,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2586,7 +2586,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2649,7 +2649,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2728,7 +2728,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2791,7 +2791,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>7</v>
@@ -2817,7 +2817,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2906,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -2969,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -2995,7 +2995,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>6</v>
@@ -3058,7 +3058,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <v>6</v>
@@ -3084,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -3147,7 +3147,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3173,7 +3173,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -3236,7 +3236,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3262,7 +3262,7 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3351,7 +3351,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3440,7 +3440,7 @@
         <v>8</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -3503,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3529,7 +3529,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3592,7 +3592,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>6</v>
@@ -3618,7 +3618,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3681,7 +3681,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3707,7 +3707,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -3770,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z35">
         <v>7</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -3859,7 +3859,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>10</v>
@@ -3927,89 +3927,92 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.3</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>26</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>81.25</v>
+      </c>
+      <c r="G3">
+        <v>18.75</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>78.79000000000001</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.3</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>21.21</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>81.25</v>
+        <v>87.88</v>
       </c>
       <c r="G4">
-        <v>18.75</v>
+        <v>12.12</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4020,28 +4023,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>87.88</v>
+        <v>93.75</v>
       </c>
       <c r="G5">
-        <v>12.12</v>
+        <v>6.25</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4055,7 +4058,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -4153,7 +4156,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4182,19 +4185,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920283</v>
+        <v>20330051920285</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -4202,19 +4205,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -4222,19 +4225,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920285</v>
+        <v>20330051920298</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -4242,39 +4245,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920285</v>
+        <v>20330051920301</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
       <c r="E5" t="s">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920286</v>
+        <v>20330051920309</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -4282,19 +4285,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920390</v>
+        <v>20330051920310</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -4302,661 +4305,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920287</v>
+        <v>20330051920379</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920290</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920292</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920293</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920294</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920394</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920295</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920296</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920297</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920297</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920298</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920298</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920299</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920301</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920301</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920303</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920304</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920307</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920308</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920309</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920309</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920310</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920310</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920211</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920311</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920216</v>
-      </c>
-      <c r="B34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920312</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920379</v>
-      </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920379</v>
-      </c>
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>146</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920313</v>
-      </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920314</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>148</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920316</v>
-      </c>
-      <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4996,16 +4359,16 @@
         <v>20330051920285</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5013,16 +4376,16 @@
         <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5030,16 +4393,16 @@
         <v>20330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5047,16 +4410,16 @@
         <v>20330051920301</v>
       </c>
       <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
         <v>81</v>
       </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>135</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5064,16 +4427,16 @@
         <v>20330051920309</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5081,16 +4444,16 @@
         <v>20330051920310</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5098,16 +4461,16 @@
         <v>20330051920379</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5115,16 +4478,16 @@
         <v>20330051920283</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5132,16 +4495,16 @@
         <v>20330051920284</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5149,16 +4512,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5166,16 +4529,16 @@
         <v>20330051920390</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5183,16 +4546,16 @@
         <v>20330051920287</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5200,16 +4563,16 @@
         <v>20330051920290</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5217,16 +4580,16 @@
         <v>20330051920292</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5234,16 +4597,16 @@
         <v>20330051920293</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5251,16 +4614,16 @@
         <v>20330051920294</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5268,16 +4631,16 @@
         <v>20330051920394</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5285,16 +4648,16 @@
         <v>20330051920295</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5302,16 +4665,16 @@
         <v>20330051920296</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5319,16 +4682,16 @@
         <v>20330051920299</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5336,16 +4699,16 @@
         <v>20330051920300</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5353,197 +4716,197 @@
         <v>20330051920303</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920304</v>
+        <v>19330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920307</v>
+        <v>20330051920304</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920308</v>
+        <v>20330051920307</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920211</v>
+        <v>20330051920308</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920311</v>
+        <v>20330051920211</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920216</v>
+        <v>20330051920311</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920312</v>
+        <v>20330051920216</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920313</v>
+        <v>20330051920312</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920314</v>
+        <v>20330051920313</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920316</v>
+        <v>20330051920314</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920208</v>
+        <v>20330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>152</v>
@@ -5559,7 +4922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5591,22 +4954,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920298</v>
+        <v>20330051920301</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5614,88 +4977,88 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920298</v>
+        <v>20330051920301</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920310</v>
+        <v>20330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920310</v>
+        <v>20330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920311</v>
+        <v>20330051920309</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -5706,19 +5069,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920311</v>
+        <v>20330051920309</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>57</v>
@@ -5729,19 +5092,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920283</v>
+        <v>20330051920379</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -5752,88 +5115,88 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920284</v>
+        <v>20330051920379</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920286</v>
+        <v>20330051920287</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920390</v>
+        <v>20330051920292</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920287</v>
+        <v>20330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
@@ -5844,42 +5207,42 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920290</v>
+        <v>19330051920208</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920292</v>
+        <v>20330051920310</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>55</v>
@@ -5890,393 +5253,25 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920293</v>
+        <v>20330051920311</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920294</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920394</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920295</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920296</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920299</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920303</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920208</v>
-      </c>
-      <c r="B23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920304</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920308</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920216</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920312</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920313</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920314</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920316</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BLCM - Estadisticos 20212.xlsx
+++ b/grupos/4BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -191,18 +191,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,259 +215,259 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>CARRASCO</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>CITLALLI</t>
   </si>
   <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
     <t>ARIADNA</t>
   </si>
   <si>
     <t>ELIAN</t>
   </si>
   <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>RITA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
     <t>SAMANTHA</t>
   </si>
   <si>
     <t>ARANTZA</t>
   </si>
   <si>
+    <t>DIANA SARAY</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>MARIA XIMENA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
     <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DIANA SARAY</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MARIA XIMENA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
   </si>
   <si>
     <t>JOSELIN GUADALUPE</t>
@@ -999,10 +999,10 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1011,13 +1011,13 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1041,10 +1041,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1056,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -1088,10 +1088,10 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1100,13 +1100,13 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1177,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1189,13 +1189,13 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1219,7 +1219,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1237,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1245,7 +1245,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1266,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1278,13 +1278,13 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1308,7 +1308,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1320,13 +1320,13 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1367,13 +1367,13 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1397,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1409,13 +1409,13 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1444,10 +1444,10 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1456,13 +1456,13 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1533,10 +1533,10 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1545,13 +1545,13 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1590,7 +1590,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1622,10 +1622,10 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1634,13 +1634,13 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1676,10 +1676,10 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1711,10 +1711,10 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1723,13 +1723,13 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1800,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1812,13 +1812,13 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1889,10 +1889,10 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1901,13 +1901,13 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1943,7 +1943,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1978,10 +1978,10 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1990,13 +1990,13 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2020,10 +2020,10 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -2067,10 +2067,10 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2079,13 +2079,13 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2112,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2124,7 +2124,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2156,10 +2156,10 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2168,13 +2168,13 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2201,7 +2201,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2210,13 +2210,13 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2224,7 +2224,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -2245,10 +2245,10 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2257,13 +2257,13 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2287,10 +2287,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2299,10 +2299,10 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2313,7 +2313,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -2334,10 +2334,10 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2346,13 +2346,13 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2376,10 +2376,10 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2391,10 +2391,10 @@
         <v>10</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2423,10 +2423,10 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2435,13 +2435,13 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2468,7 +2468,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2480,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>10</v>
@@ -2512,10 +2512,10 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2524,13 +2524,13 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2566,10 +2566,10 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2580,7 +2580,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2601,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2613,13 +2613,13 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2643,7 +2643,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2655,13 +2655,13 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2681,16 +2681,16 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2705,16 +2705,16 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2743,10 +2743,10 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2755,13 +2755,13 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2785,10 +2785,10 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2832,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2844,13 +2844,13 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2874,7 +2874,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2886,13 +2886,13 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2921,10 +2921,10 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2933,13 +2933,13 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2989,7 +2989,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -3010,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -3022,13 +3022,13 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3052,7 +3052,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -3064,13 +3064,13 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3078,7 +3078,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>8</v>
@@ -3099,10 +3099,10 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3111,13 +3111,13 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3141,10 +3141,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3153,13 +3153,13 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3188,10 +3188,10 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3200,13 +3200,13 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3233,7 +3233,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -3248,7 +3248,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3277,10 +3277,10 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3289,13 +3289,13 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3366,10 +3366,10 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3378,13 +3378,13 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3434,7 +3434,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -3455,10 +3455,10 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3467,13 +3467,13 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3497,7 +3497,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3509,10 +3509,10 @@
         <v>5</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3544,7 +3544,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3556,13 +3556,13 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3586,7 +3586,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3601,7 +3601,7 @@
         <v>9</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>10</v>
@@ -3633,10 +3633,10 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3645,13 +3645,13 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3675,10 +3675,10 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3693,7 +3693,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3722,10 +3722,10 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3734,13 +3734,13 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3764,7 +3764,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3811,10 +3811,10 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3823,13 +3823,13 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3865,10 +3865,10 @@
         <v>10</v>
       </c>
       <c r="AA36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>10</v>
@@ -3936,25 +3936,25 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>78.79000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3991,28 +3991,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>87.88</v>
+        <v>93.75</v>
       </c>
       <c r="G4">
-        <v>12.12</v>
+        <v>6.25</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4023,28 +4023,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
         <v>32</v>
       </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>93.75</v>
+        <v>96.97</v>
       </c>
       <c r="G5">
-        <v>6.25</v>
+        <v>3.03</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4055,28 +4055,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4087,28 +4087,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>33</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4119,16 +4119,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
       </c>
       <c r="C8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4156,7 +4156,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4181,146 +4181,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920285</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920297</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920298</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920301</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920309</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920310</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920379</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4356,132 +4216,132 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920285</v>
+        <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920297</v>
+        <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920298</v>
+        <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920301</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920309</v>
+        <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920310</v>
+        <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920379</v>
+        <v>20330051920290</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920283</v>
+        <v>20330051920292</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>127</v>
@@ -4492,13 +4352,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920284</v>
+        <v>20330051920293</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
         <v>128</v>
@@ -4509,13 +4369,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920286</v>
+        <v>20330051920294</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>129</v>
@@ -4526,13 +4386,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920390</v>
+        <v>20330051920394</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>130</v>
@@ -4543,13 +4403,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920287</v>
+        <v>20330051920295</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
         <v>131</v>
@@ -4560,13 +4420,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920290</v>
+        <v>20330051920296</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>132</v>
@@ -4577,13 +4437,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920292</v>
+        <v>20330051920297</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -4594,13 +4454,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920293</v>
+        <v>20330051920298</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>134</v>
@@ -4611,13 +4471,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920294</v>
+        <v>20330051920299</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
         <v>135</v>
@@ -4628,13 +4488,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920394</v>
+        <v>20330051920300</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>136</v>
@@ -4645,13 +4505,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920295</v>
+        <v>20330051920301</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>137</v>
@@ -4662,13 +4522,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920296</v>
+        <v>20330051920303</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>138</v>
@@ -4679,13 +4539,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920299</v>
+        <v>19330051920208</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
         <v>139</v>
@@ -4696,13 +4556,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920300</v>
+        <v>20330051920304</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
         <v>140</v>
@@ -4713,13 +4573,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920303</v>
+        <v>20330051920307</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>141</v>
@@ -4730,13 +4590,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920208</v>
+        <v>20330051920308</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
         <v>142</v>
@@ -4747,13 +4607,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920304</v>
+        <v>20330051920309</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>143</v>
@@ -4764,13 +4624,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920307</v>
+        <v>20330051920310</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
         <v>144</v>
@@ -4781,13 +4641,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920308</v>
+        <v>20330051920211</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -4798,13 +4658,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920211</v>
+        <v>20330051920311</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -4815,13 +4675,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920311</v>
+        <v>20330051920216</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>147</v>
@@ -4832,13 +4692,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920216</v>
+        <v>20330051920312</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
         <v>148</v>
@@ -4849,13 +4709,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920312</v>
+        <v>20330051920379</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
         <v>149</v>
@@ -4869,10 +4729,10 @@
         <v>20330051920313</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
         <v>150</v>
@@ -4886,10 +4746,10 @@
         <v>20330051920314</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
         <v>151</v>
@@ -4903,10 +4763,10 @@
         <v>20330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>152</v>
@@ -4922,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4954,16 +4814,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920301</v>
+        <v>20330051920285</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4972,21 +4832,21 @@
         <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920301</v>
+        <v>20330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5000,22 +4860,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920307</v>
+        <v>20330051920287</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5023,19 +4883,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920307</v>
+        <v>20330051920287</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>57</v>
@@ -5046,16 +4906,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920309</v>
+        <v>20330051920301</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5064,27 +4924,27 @@
         <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920309</v>
+        <v>20330051920301</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5092,16 +4952,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920379</v>
+        <v>20330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5110,21 +4970,21 @@
         <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920379</v>
+        <v>20330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5138,22 +4998,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920287</v>
+        <v>20330051920379</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5161,22 +5021,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920292</v>
+        <v>20330051920379</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5184,45 +5044,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920298</v>
+        <v>20330051920292</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920208</v>
+        <v>20330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5230,16 +5090,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920310</v>
+        <v>19330051920208</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5248,29 +5108,75 @@
         <v>55</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>20330051920309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920310</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>20330051920311</v>
       </c>
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>56</v>
       </c>
-      <c r="G15">
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20212.xlsx
+++ b/grupos/4BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -185,13 +185,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Ángel Martínez Noe Cristobal</t>
@@ -1005,10 +1005,10 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -1047,10 +1047,10 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>9</v>
@@ -1094,10 +1094,10 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1136,10 +1136,10 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1183,10 +1183,10 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1225,10 +1225,10 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1272,10 +1272,10 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1314,7 +1314,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1361,10 +1361,10 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1406,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>8</v>
@@ -1450,10 +1450,10 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1492,7 +1492,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>10</v>
@@ -1539,10 +1539,10 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1628,10 +1628,10 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1717,10 +1717,10 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1806,10 +1806,10 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1895,10 +1895,10 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -1937,10 +1937,10 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1984,10 +1984,10 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -2026,7 +2026,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -2073,10 +2073,10 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -2115,10 +2115,10 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2162,10 +2162,10 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2204,10 +2204,10 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2251,10 +2251,10 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>9</v>
@@ -2293,7 +2293,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2340,10 +2340,10 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2382,7 +2382,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2429,10 +2429,10 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2471,10 +2471,10 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -2518,10 +2518,10 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2560,7 +2560,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2607,10 +2607,10 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2649,7 +2649,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2749,10 +2749,10 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2791,10 +2791,10 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2838,10 +2838,10 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2927,10 +2927,10 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2969,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -3016,10 +3016,10 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -3058,10 +3058,10 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3105,10 +3105,10 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -3147,10 +3147,10 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3194,10 +3194,10 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -3236,10 +3236,10 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>10</v>
@@ -3283,10 +3283,10 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3372,10 +3372,10 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3461,10 +3461,10 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -3503,10 +3503,10 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -3550,10 +3550,10 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -3639,10 +3639,10 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3681,10 +3681,10 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>10</v>
@@ -3728,10 +3728,10 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3770,10 +3770,10 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>10</v>
@@ -3817,10 +3817,10 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3859,10 +3859,10 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA36">
         <v>10</v>
@@ -3927,28 +3927,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
         <v>23</v>
       </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
       <c r="F2">
-        <v>69.7</v>
+        <v>28.13</v>
       </c>
       <c r="G2">
-        <v>30.3</v>
+        <v>71.88</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3959,28 +3959,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>81.25</v>
+        <v>69.7</v>
       </c>
       <c r="G3">
-        <v>18.75</v>
+        <v>30.3</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -4000,19 +4000,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>93.75</v>
+        <v>71.88</v>
       </c>
       <c r="G4">
-        <v>6.25</v>
+        <v>28.13</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4782,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4829,7 +4829,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4852,7 +4852,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4860,19 +4860,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920287</v>
+        <v>20330051920286</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -4883,19 +4883,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920287</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>57</v>
@@ -4906,22 +4906,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920301</v>
+        <v>20330051920287</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920301</v>
+        <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4952,19 +4952,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920307</v>
+        <v>20330051920293</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920307</v>
+        <v>20330051920293</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4998,22 +4998,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920379</v>
+        <v>20330051920298</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5021,22 +5021,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920379</v>
+        <v>20330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5044,22 +5044,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920292</v>
+        <v>20330051920310</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920298</v>
+        <v>20330051920310</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5090,19 +5090,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920208</v>
+        <v>20330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>55</v>
@@ -5113,22 +5113,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920309</v>
+        <v>20330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920310</v>
+        <v>20330051920379</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5159,24 +5159,346 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920311</v>
+        <v>20330051920379</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920283</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920284</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920390</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920292</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920394</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920296</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920299</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920300</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920303</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>19330051920208</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
         <v>56</v>
       </c>
-      <c r="G17">
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920308</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920313</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920314</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920316</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20212.xlsx
+++ b/grupos/4BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -185,22 +185,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
     <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
     <t>NC</t>
@@ -1005,7 +1005,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1029,16 +1029,16 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -1047,19 +1047,19 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1094,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1118,16 +1118,16 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1136,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -1183,7 +1183,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1198,7 +1198,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1207,16 +1207,16 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1225,16 +1225,16 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1287,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1296,37 +1296,37 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1361,7 +1361,7 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1385,16 +1385,16 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1403,19 +1403,19 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1450,7 +1450,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1474,16 +1474,16 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1492,13 +1492,13 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1539,7 +1539,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1554,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1563,16 +1563,16 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1581,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1628,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1643,7 +1643,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1652,25 +1652,25 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1717,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1732,7 +1732,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1741,16 +1741,16 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1759,10 +1759,10 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1830,16 +1830,16 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1857,10 +1857,10 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1895,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1910,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1919,28 +1919,28 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1999,7 +1999,7 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2008,16 +2008,16 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -2026,19 +2026,19 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2073,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2097,16 +2097,16 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2115,19 +2115,19 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2162,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2177,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2186,16 +2186,16 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2204,7 +2204,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2266,7 +2266,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2275,16 +2275,16 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2293,10 +2293,10 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2305,7 +2305,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2340,7 +2340,7 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2355,7 +2355,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2364,28 +2364,28 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2429,7 +2429,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2453,37 +2453,37 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2518,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2542,25 +2542,25 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2569,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2607,7 +2607,7 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2622,7 +2622,7 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2631,28 +2631,28 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>9</v>
@@ -2693,19 +2693,19 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2714,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2749,7 +2749,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2773,16 +2773,16 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2791,7 +2791,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2838,7 +2838,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2853,7 +2853,7 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2862,28 +2862,28 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>8</v>
@@ -2927,7 +2927,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2942,7 +2942,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2951,16 +2951,16 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2969,19 +2969,19 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3016,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -3040,28 +3040,28 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3105,7 +3105,7 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -3120,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3129,16 +3129,16 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3147,10 +3147,10 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3159,7 +3159,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3194,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -3209,7 +3209,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3218,37 +3218,37 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3283,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3298,7 +3298,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3307,25 +3307,25 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3372,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3387,7 +3387,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3396,16 +3396,16 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3414,10 +3414,10 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3461,7 +3461,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3485,16 +3485,16 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3503,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>8</v>
@@ -3550,7 +3550,7 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -3565,7 +3565,7 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3574,16 +3574,16 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -3639,7 +3639,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -3654,7 +3654,7 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3663,31 +3663,31 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>8</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>9</v>
@@ -3728,7 +3728,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>8</v>
@@ -3743,7 +3743,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3752,16 +3752,16 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3770,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>8</v>
@@ -3817,7 +3817,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -3832,7 +3832,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3841,37 +3841,37 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z36">
         <v>9</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3927,28 +3927,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>28.13</v>
+        <v>87.88</v>
       </c>
       <c r="G2">
-        <v>71.88</v>
+        <v>12.12</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3968,19 +3968,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>69.7</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -4000,19 +4000,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4023,28 +4023,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4087,16 +4087,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4119,16 +4119,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4782,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920285</v>
+        <v>20330051920287</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920285</v>
+        <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4860,19 +4860,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920286</v>
+        <v>20330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -4883,622 +4883,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920286</v>
+        <v>20330051920379</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920287</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920287</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920293</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920293</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920298</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920298</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920310</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920310</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920312</v>
-      </c>
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920312</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920379</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920379</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920283</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920284</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920390</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920292</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920394</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920296</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920299</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920300</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920303</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920208</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920308</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920313</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920314</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920316</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20212.xlsx
+++ b/grupos/4BLCM - Estadisticos 20212.xlsx
@@ -1023,10 +1023,10 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -1112,10 +1112,10 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1201,10 +1201,10 @@
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1290,10 +1290,10 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1379,10 +1379,10 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>6</v>
@@ -1400,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1468,10 +1468,10 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1489,7 +1489,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1557,10 +1557,10 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1646,10 +1646,10 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1667,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1735,10 +1735,10 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1759,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1824,10 +1824,10 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1913,10 +1913,10 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -2002,10 +2002,10 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -2023,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -2091,10 +2091,10 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>6</v>
@@ -2112,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -2180,10 +2180,10 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -2201,10 +2201,10 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2269,10 +2269,10 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>8</v>
@@ -2290,7 +2290,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2358,10 +2358,10 @@
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -2379,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2447,10 +2447,10 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2536,10 +2536,10 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2557,7 +2557,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2604,7 +2604,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2625,10 +2625,10 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2646,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -2696,7 +2696,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2708,7 +2708,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -2767,10 +2767,10 @@
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -2791,7 +2791,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2835,7 +2835,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -2856,10 +2856,10 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -2877,7 +2877,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2945,10 +2945,10 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -3013,7 +3013,7 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -3034,10 +3034,10 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -3123,10 +3123,10 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -3144,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -3212,10 +3212,10 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -3301,10 +3301,10 @@
         <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>10</v>
@@ -3390,10 +3390,10 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>7</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>9</v>
@@ -3479,10 +3479,10 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3547,7 +3547,7 @@
         <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -3568,10 +3568,10 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>7</v>
@@ -3589,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3657,10 +3657,10 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3746,10 +3746,10 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3835,10 +3835,10 @@
         <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>8</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
